--- a/v3/OG0005/OG0005_DevSpec.xlsx
+++ b/v3/OG0005/OG0005_DevSpec.xlsx
@@ -1279,7 +1279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>the box</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>up</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>picked</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>picked</t>
+          <t>He</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -1813,21 +1813,25 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>OG0005_V3_Q04</t>
+          <t>OG0005_V3_Q05</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>He</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr"/>
+          <t>disappointed</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E25" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="F25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1838,21 +1842,25 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>disappointed</t>
+          <t>proud</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E26" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>포획 직후 감정을 문제 장면에 적용합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1862,23 +1870,23 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>proud</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>포획 직후 감정을 문제 장면에 적용합니다.</t>
+          <t>부정 감정은 파악했으나 실망과 분노를 혼동합니다.</t>
         </is>
       </c>
     </row>
@@ -1890,53 +1898,49 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>sleepy</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>부정 감정은 파악했으나 실망과 분노를 혼동합니다.</t>
+          <t>장면의 문제 상황을 놓칩니다.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>OG0005_V3_Q05</t>
+          <t>OG0005_V3_Q06</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>sleepy</t>
+          <t>I made a mistake.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>장면의 문제 상황을 놓칩니다.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1946,21 +1950,25 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>I made a mistake.</t>
+          <t>I need a bigger box.</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>문제의 원인을 소유가 아닌 도구로 오해합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1970,23 +1978,23 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>I need a bigger box.</t>
+          <t>The cloud is mine forever.</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>문제의 원인을 소유가 아닌 도구로 오해합니다.</t>
+          <t>인물의 깨달음과 반대되는 생각을 선택합니다.</t>
         </is>
       </c>
     </row>
@@ -1998,49 +2006,21 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>The cloud is mine forever.</t>
+          <t>Podo should go away.</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>인물의 깨달음과 반대되는 생각을 선택합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>OG0005_V3_Q06</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Podo should go away.</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>친구의 조언을 내면 변화와 연결하지 못합니다.</t>
         </is>
@@ -2057,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2561,7 +2541,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>the box</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -2590,7 +2570,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>and</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -2619,7 +2599,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>ran</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -2648,7 +2628,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ran</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -2677,11 +2657,11 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>outside.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -2701,29 +2681,29 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>OG0005_V3_Q04</t>
+          <t>OG0005_V3_Q05</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>outside.</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2.5</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>exact_position</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>9</v>
+          <t>option_score</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Actor/action/result word order.</t>
+          <t>Correct reaction/emotion.</t>
         </is>
       </c>
     </row>
@@ -2735,11 +2715,11 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -2747,12 +2727,12 @@
         </is>
       </c>
       <c r="E23" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Correct reaction/emotion.</t>
+          <t>포획 직후 감정을 문제 장면에 적용합니다.</t>
         </is>
       </c>
     </row>
@@ -2764,11 +2744,11 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
@@ -2781,7 +2761,7 @@
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>포획 직후 감정을 문제 장면에 적용합니다.</t>
+          <t>부정 감정은 파악했으나 실망과 분노를 혼동합니다.</t>
         </is>
       </c>
     </row>
@@ -2793,11 +2773,11 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
@@ -2810,23 +2790,23 @@
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>부정 감정은 파악했으나 실망과 분노를 혼동합니다.</t>
+          <t>장면의 문제 상황을 놓칩니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>OG0005_V3_Q05</t>
+          <t>OG0005_V3_Q06</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
@@ -2834,12 +2814,12 @@
         </is>
       </c>
       <c r="E26" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>장면의 문제 상황을 놓칩니다.</t>
+          <t>Correct internal response.</t>
         </is>
       </c>
     </row>
@@ -2851,11 +2831,11 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
@@ -2863,12 +2843,12 @@
         </is>
       </c>
       <c r="E27" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Correct internal response.</t>
+          <t>문제의 원인을 소유가 아닌 도구로 오해합니다.</t>
         </is>
       </c>
     </row>
@@ -2880,11 +2860,11 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
@@ -2897,7 +2877,7 @@
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>문제의 원인을 소유가 아닌 도구로 오해합니다.</t>
+          <t>인물의 깨달음과 반대되는 생각을 선택합니다.</t>
         </is>
       </c>
     </row>
@@ -2909,11 +2889,11 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
@@ -2925,35 +2905,6 @@
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>인물의 깨달음과 반대되는 생각을 선택합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>OG0005_V3_Q06</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>option_score</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>친구의 조언을 내면 변화와 연결하지 못합니다.</t>
         </is>
